--- a/data/trans_bre/IP04D$individual-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP04D$individual-Clase-trans_bre.xlsx
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-23,63; -1,04</t>
+          <t>-24,36; 0,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 15,88</t>
+          <t>-7,03; 15,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,2; 5,94</t>
+          <t>-13,86; 5,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-44,18; -2,2</t>
+          <t>-44,7; 0,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-16,75; 50,52</t>
+          <t>-16,74; 51,1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-44,89; 28,09</t>
+          <t>-43,05; 21,86</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-17,77; 6,15</t>
+          <t>-16,16; 7,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-16,63; 5,68</t>
+          <t>-15,21; 6,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-12,51; 8,81</t>
+          <t>-12,51; 8,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-35,5; 15,51</t>
+          <t>-33,47; 21,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-34,66; 15,6</t>
+          <t>-33,81; 19,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-43,84; 47,55</t>
+          <t>-42,69; 47,02</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,09; 11,84</t>
+          <t>-11,02; 11,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-16,57; 10,01</t>
+          <t>-16,47; 9,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,42; 8,88</t>
+          <t>-10,66; 10,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-31,49; 49,53</t>
+          <t>-31,57; 51,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-39,41; 31,25</t>
+          <t>-35,95; 29,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-66,96; 124,22</t>
+          <t>-64,07; 141,7</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,4; 3,88</t>
+          <t>-9,68; 4,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 12,45</t>
+          <t>-1,26; 12,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-16,01; -0,53</t>
+          <t>-15,48; 0,08</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-31,27; 15,38</t>
+          <t>-29,73; 19,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 55,1</t>
+          <t>-4,3; 58,38</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-62,27; -2,72</t>
+          <t>-61,19; 0,49</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-13,94; 3,58</t>
+          <t>-15,4; 2,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 8,6</t>
+          <t>-7,78; 7,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-22,96; 3,01</t>
+          <t>-23,51; 3,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-42,31; 16,66</t>
+          <t>-46,35; 11,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-31,94; 57,84</t>
+          <t>-34,41; 51,23</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-75,77; 29,68</t>
+          <t>-78,02; 33,36</t>
         </is>
       </c>
     </row>
@@ -1032,32 +1032,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-13,5; 10,15</t>
+          <t>-13,34; 10,47</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 20,1</t>
+          <t>-5,46; 20,95</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-8,1; 14,72</t>
+          <t>-8,63; 13,94</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-50,14; 63,81</t>
+          <t>-48,75; 60,37</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-20,75; 141,52</t>
+          <t>-21,29; 150,87</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-44,57; 180,4</t>
+          <t>-49,15; 164,15</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,11; -0,43</t>
+          <t>-8,7; -0,4</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 5,7</t>
+          <t>-2,36; 5,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,46; -0,35</t>
+          <t>-9,54; -0,64</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-23,63; -0,79</t>
+          <t>-25,11; -1,34</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,31; 21,13</t>
+          <t>-7,4; 20,56</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-39,12; -1,59</t>
+          <t>-39,77; -3,11</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP04D$individual-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP04D$individual-Clase-trans_bre.xlsx
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-24,36; 0,07</t>
+          <t>-25,7; -0,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,03; 15,62</t>
+          <t>-7,27; 15,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,86; 5,02</t>
+          <t>-14,37; 4,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-44,7; 0,02</t>
+          <t>-47,66; 0,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-16,74; 51,1</t>
+          <t>-17,89; 49,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-43,05; 21,86</t>
+          <t>-42,93; 22,5</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-16,16; 7,86</t>
+          <t>-16,95; 6,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-15,21; 6,66</t>
+          <t>-15,66; 5,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-12,51; 8,4</t>
+          <t>-13,69; 7,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-33,47; 21,07</t>
+          <t>-34,93; 17,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-33,81; 19,04</t>
+          <t>-33,49; 14,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-42,69; 47,02</t>
+          <t>-43,52; 39,29</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,02; 11,78</t>
+          <t>-10,84; 11,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-16,47; 9,36</t>
+          <t>-15,81; 11,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,66; 10,91</t>
+          <t>-12,45; 9,03</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-31,57; 51,0</t>
+          <t>-31,9; 49,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-35,95; 29,59</t>
+          <t>-36,47; 39,2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-64,07; 141,7</t>
+          <t>-70,7; 134,96</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,68; 4,64</t>
+          <t>-9,65; 4,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 12,76</t>
+          <t>-1,22; 13,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-15,48; 0,08</t>
+          <t>-15,93; -0,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-29,73; 19,25</t>
+          <t>-30,51; 19,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 58,38</t>
+          <t>-4,58; 58,72</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-61,19; 0,49</t>
+          <t>-62,94; -1,82</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-15,4; 2,73</t>
+          <t>-13,62; 2,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,78; 7,54</t>
+          <t>-7,78; 7,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-23,51; 3,25</t>
+          <t>-26,03; 2,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-46,35; 11,48</t>
+          <t>-42,23; 13,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-34,41; 51,23</t>
+          <t>-34,86; 49,98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-78,02; 33,36</t>
+          <t>-77,44; 23,79</t>
         </is>
       </c>
     </row>
@@ -1032,32 +1032,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-13,34; 10,47</t>
+          <t>-12,92; 10,51</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 20,95</t>
+          <t>-4,55; 20,62</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-8,63; 13,94</t>
+          <t>-7,67; 14,96</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-48,75; 60,37</t>
+          <t>-49,02; 60,6</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-21,29; 150,87</t>
+          <t>-17,97; 145,84</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-49,15; 164,15</t>
+          <t>-42,73; 183,53</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,7; -0,4</t>
+          <t>-8,01; -0,11</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 5,54</t>
+          <t>-2,49; 5,93</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,54; -0,64</t>
+          <t>-9,02; -0,17</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-25,11; -1,34</t>
+          <t>-23,18; -0,26</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,4; 20,56</t>
+          <t>-8,03; 21,84</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-39,77; -3,11</t>
+          <t>-38,86; -0,5</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP04D$individual-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP04D$individual-Clase-trans_bre.xlsx
@@ -518,8 +518,10 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Población que dispone de calefacción individual en su vivienda</t>
+        </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
@@ -604,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-4,69</t>
+          <t>-5,59</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -619,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-16,76%</t>
+          <t>-19,05%</t>
         </is>
       </c>
     </row>
@@ -632,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-25,7; -0,07</t>
+          <t>-23,63; -1,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,27; 15,88</t>
+          <t>-6,47; 15,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,37; 4,99</t>
+          <t>-15,74; 5,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-47,66; 0,36</t>
+          <t>-44,18; -2,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-17,89; 49,94</t>
+          <t>-16,75; 50,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-42,93; 22,5</t>
+          <t>-45,97; 24,36</t>
         </is>
       </c>
     </row>
@@ -684,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-2,03</t>
+          <t>-2,43</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -699,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-8,39%</t>
+          <t>-10,3%</t>
         </is>
       </c>
     </row>
@@ -712,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-16,95; 6,69</t>
+          <t>-17,77; 6,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-15,66; 5,29</t>
+          <t>-16,63; 5,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-13,69; 7,59</t>
+          <t>-13,21; 8,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-34,93; 17,94</t>
+          <t>-35,5; 15,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-33,49; 14,5</t>
+          <t>-34,66; 15,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-43,52; 39,29</t>
+          <t>-46,16; 45,48</t>
         </is>
       </c>
     </row>
@@ -764,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,97</t>
+          <t>-1,63</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -779,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-7,96%</t>
+          <t>-13,04%</t>
         </is>
       </c>
     </row>
@@ -792,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,84; 11,47</t>
+          <t>-11,09; 11,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-15,81; 11,26</t>
+          <t>-16,57; 10,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,45; 9,03</t>
+          <t>-12,04; 8,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-31,9; 49,83</t>
+          <t>-31,49; 49,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-36,47; 39,2</t>
+          <t>-39,41; 31,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-70,7; 134,96</t>
+          <t>-69,54; 112,91</t>
         </is>
       </c>
     </row>
@@ -844,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-7,29</t>
+          <t>-4,78</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -859,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-34,73%</t>
+          <t>-22,83%</t>
         </is>
       </c>
     </row>
@@ -872,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,65; 4,68</t>
+          <t>-10,4; 3,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 13,12</t>
+          <t>-1,56; 12,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-15,93; -0,32</t>
+          <t>-12,54; 2,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-30,51; 19,02</t>
+          <t>-31,27; 15,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 58,72</t>
+          <t>-5,34; 55,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-62,94; -1,82</t>
+          <t>-49,25; 13,44</t>
         </is>
       </c>
     </row>
@@ -924,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-6,28</t>
+          <t>-5,87</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -939,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-35,05%</t>
+          <t>-33,55%</t>
         </is>
       </c>
     </row>
@@ -952,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-13,62; 2,88</t>
+          <t>-13,94; 3,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,78; 7,62</t>
+          <t>-7,32; 8,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-26,03; 2,43</t>
+          <t>-21,03; 2,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-42,23; 13,21</t>
+          <t>-42,31; 16,66</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-34,86; 49,98</t>
+          <t>-31,94; 57,84</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-77,44; 23,79</t>
+          <t>-74,56; 29,05</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1006,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2,98</t>
+          <t>4,27</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1019,7 +1021,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>31,59%</t>
         </is>
       </c>
     </row>
@@ -1032,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-12,92; 10,51</t>
+          <t>-13,5; 10,15</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 20,62</t>
+          <t>-5,27; 20,1</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-7,67; 14,96</t>
+          <t>-7,09; 16,2</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-49,02; 60,6</t>
+          <t>-50,14; 63,81</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-17,97; 145,84</t>
+          <t>-20,75; 141,52</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-42,73; 183,53</t>
+          <t>-40,52; 199,22</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1086,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-4,36</t>
+          <t>-3,53</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1099,7 +1101,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-21,19%</t>
+          <t>-17,15%</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,01; -0,11</t>
+          <t>-8,11; -0,43</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 5,93</t>
+          <t>-2,47; 5,7</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,02; -0,17</t>
+          <t>-8,18; 0,57</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-23,18; -0,26</t>
+          <t>-23,63; -0,79</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,03; 21,84</t>
+          <t>-8,31; 21,13</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-38,86; -0,5</t>
+          <t>-35,14; 3,19</t>
         </is>
       </c>
     </row>
